--- a/public/upload/export_excel/all-07-2025.xlsx
+++ b/public/upload/export_excel/all-07-2025.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="38">
   <si>
     <t>สาขาเจริญใจ</t>
   </si>
@@ -89,16 +89,46 @@
     <t>เบอร์โทร</t>
   </si>
   <si>
+    <t>A105</t>
+  </si>
+  <si>
+    <t>5,249</t>
+  </si>
+  <si>
+    <t>สุรีย์พร รัตนา</t>
+  </si>
+  <si>
+    <t>ต.ทรายกองดินใต้ อ.เขต คลองสามวา จ.กรุงเทพมหานคร</t>
+  </si>
+  <si>
+    <t>A104</t>
+  </si>
+  <si>
+    <t>6,570</t>
+  </si>
+  <si>
+    <t>นฤมาศ วิชาญ</t>
+  </si>
+  <si>
+    <t>ต.ปลายพระยา อ.ปลายพระยา จ.กระบี่</t>
+  </si>
+  <si>
+    <t>A103</t>
+  </si>
+  <si>
+    <t>6,032</t>
+  </si>
+  <si>
     <t>A102</t>
   </si>
   <si>
-    <t>5,824</t>
-  </si>
-  <si>
-    <t>ธนพล วรินทร</t>
-  </si>
-  <si>
-    <t>ต.ทรายกองดินใต้ อ.เขต คลองสามวา จ.กรุงเทพมหานคร</t>
+    <t>6,055</t>
+  </si>
+  <si>
+    <t>A101</t>
+  </si>
+  <si>
+    <t>6,064</t>
   </si>
 </sst>
 </file>
@@ -441,7 +471,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:V4"/>
+  <dimension ref="A1:V8"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" spans="1:22">
@@ -571,9 +601,11 @@
       <c r="B4" s="1">
         <v>5000</v>
       </c>
-      <c r="C4" s="1"/>
+      <c r="C4" s="1">
+        <v>0</v>
+      </c>
       <c r="D4" s="1">
-        <v>224</v>
+        <v>49</v>
       </c>
       <c r="E4" s="1">
         <v>300.0</v>
@@ -582,19 +614,19 @@
         <v>500.0</v>
       </c>
       <c r="G4" s="1">
-        <v>100.0</v>
+        <v>0.0</v>
       </c>
       <c r="H4" s="1">
-        <v>500.0</v>
+        <v>0.0</v>
       </c>
       <c r="I4" s="1">
-        <v>150.0</v>
+        <v>0.0</v>
       </c>
       <c r="J4" s="1">
-        <v>20.0</v>
+        <v>0.0</v>
       </c>
       <c r="K4" s="1">
-        <v>20.0</v>
+        <v>0.0</v>
       </c>
       <c r="L4" s="1" t="s">
         <v>25</v>
@@ -602,11 +634,11 @@
       <c r="M4" s="1"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="P4" s="1"/>
       <c r="Q4" s="1">
-        <v>1366</v>
+        <v>657</v>
       </c>
       <c r="R4" s="1" t="s">
         <v>26</v>
@@ -617,6 +649,238 @@
       <c r="T4" s="1"/>
       <c r="U4" s="1"/>
       <c r="V4" s="1">
+        <v>4854746554</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22">
+      <c r="A5" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" s="1">
+        <v>5000</v>
+      </c>
+      <c r="C5" s="1">
+        <v>0</v>
+      </c>
+      <c r="D5" s="1">
+        <v>320</v>
+      </c>
+      <c r="E5" s="1">
+        <v>300.0</v>
+      </c>
+      <c r="F5" s="1">
+        <v>500.0</v>
+      </c>
+      <c r="G5" s="1">
+        <v>500.0</v>
+      </c>
+      <c r="H5" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="I5" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="J5" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="K5" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="M5" s="1"/>
+      <c r="N5" s="1"/>
+      <c r="O5" s="1">
+        <v>6</v>
+      </c>
+      <c r="P5" s="1"/>
+      <c r="Q5" s="1">
+        <v>471</v>
+      </c>
+      <c r="R5" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="S5" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="T5" s="1"/>
+      <c r="U5" s="1"/>
+      <c r="V5" s="1">
+        <v>1111111111</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22">
+      <c r="A6" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" s="1">
+        <v>5000</v>
+      </c>
+      <c r="C6" s="1">
+        <v>0</v>
+      </c>
+      <c r="D6" s="1">
+        <v>1032</v>
+      </c>
+      <c r="E6" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="F6" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G6" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="H6" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="I6" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="J6" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="K6" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="M6" s="1"/>
+      <c r="N6" s="1"/>
+      <c r="O6" s="1">
+        <v>3</v>
+      </c>
+      <c r="P6" s="1"/>
+      <c r="Q6" s="1">
+        <v>1677</v>
+      </c>
+      <c r="R6" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="S6" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="T6" s="1"/>
+      <c r="U6" s="1"/>
+      <c r="V6" s="1">
+        <v>1111111111</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22">
+      <c r="A7" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B7" s="1">
+        <v>5000</v>
+      </c>
+      <c r="C7" s="1">
+        <v>0</v>
+      </c>
+      <c r="D7" s="1">
+        <v>455</v>
+      </c>
+      <c r="E7" s="1">
+        <v>100.0</v>
+      </c>
+      <c r="F7" s="1">
+        <v>500.0</v>
+      </c>
+      <c r="G7" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="H7" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="I7" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="J7" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="K7" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="M7" s="1"/>
+      <c r="N7" s="1"/>
+      <c r="O7" s="1">
+        <v>10</v>
+      </c>
+      <c r="P7" s="1"/>
+      <c r="Q7" s="1">
+        <v>1400</v>
+      </c>
+      <c r="R7" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="S7" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="T7" s="1"/>
+      <c r="U7" s="1"/>
+      <c r="V7" s="1">
+        <v>1111111111</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22">
+      <c r="A8" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B8" s="1">
+        <v>5000</v>
+      </c>
+      <c r="C8" s="1">
+        <v>104</v>
+      </c>
+      <c r="D8" s="1">
+        <v>360</v>
+      </c>
+      <c r="E8" s="1">
+        <v>100.0</v>
+      </c>
+      <c r="F8" s="1">
+        <v>500.0</v>
+      </c>
+      <c r="G8" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="H8" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="I8" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="J8" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="K8" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="M8" s="1"/>
+      <c r="N8" s="1"/>
+      <c r="O8" s="1">
+        <v>113</v>
+      </c>
+      <c r="P8" s="1"/>
+      <c r="Q8" s="1">
+        <v>1493</v>
+      </c>
+      <c r="R8" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="S8" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="T8" s="1"/>
+      <c r="U8" s="1"/>
+      <c r="V8" s="1">
         <v>1111111111</v>
       </c>
     </row>

--- a/public/upload/export_excel/all-07-2025.xlsx
+++ b/public/upload/export_excel/all-07-2025.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="78">
   <si>
     <t>สาขาเจริญใจ</t>
   </si>
@@ -54,6 +54,9 @@
   </si>
   <si>
     <t>บริการ</t>
+  </si>
+  <si>
+    <t>ค่าปรับ</t>
   </si>
   <si>
     <t>รวม</t>
@@ -588,10 +591,10 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:V23"/>
+  <dimension ref="A1:W23"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" spans="1:22">
+    <row r="1" spans="1:23">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -616,8 +619,9 @@
       <c r="T1" s="1"/>
       <c r="U1" s="1"/>
       <c r="V1" s="1"/>
-    </row>
-    <row r="2" spans="1:22">
+      <c r="W1" s="1"/>
+    </row>
+    <row r="2" spans="1:23">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -642,8 +646,9 @@
       <c r="T2" s="1"/>
       <c r="U2" s="1"/>
       <c r="V2" s="1"/>
-    </row>
-    <row r="3" spans="1:22">
+      <c r="W2" s="1"/>
+    </row>
+    <row r="3" spans="1:23">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -710,10 +715,13 @@
       <c r="V3" s="1" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="4" spans="1:22">
+      <c r="W3" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23">
       <c r="A4" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B4" s="1">
         <v>3000</v>
@@ -745,31 +753,42 @@
       <c r="K4" s="1">
         <v>0.0</v>
       </c>
-      <c r="L4" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="M4" s="1"/>
-      <c r="N4" s="1"/>
-      <c r="O4" s="1"/>
-      <c r="P4" s="1"/>
+      <c r="L4" s="1">
+        <v>0</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="N4" s="1">
+        <v>0</v>
+      </c>
+      <c r="O4" s="1">
+        <v>0</v>
+      </c>
+      <c r="P4" s="1">
+        <v>0</v>
+      </c>
       <c r="Q4" s="1">
+        <v>0</v>
+      </c>
+      <c r="R4" s="1">
         <v>1027</v>
-      </c>
-      <c r="R4" s="1" t="s">
-        <v>26</v>
       </c>
       <c r="S4" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="T4" s="1"/>
+      <c r="T4" s="1" t="s">
+        <v>28</v>
+      </c>
       <c r="U4" s="1"/>
-      <c r="V4" s="1">
+      <c r="V4" s="1"/>
+      <c r="W4" s="1">
         <v>1234567898</v>
       </c>
     </row>
-    <row r="5" spans="1:22">
+    <row r="5" spans="1:23">
       <c r="A5" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B5" s="1">
         <v>3000</v>
@@ -801,31 +820,42 @@
       <c r="K5" s="1">
         <v>0.0</v>
       </c>
-      <c r="L5" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="M5" s="1"/>
-      <c r="N5" s="1"/>
-      <c r="O5" s="1"/>
-      <c r="P5" s="1"/>
+      <c r="L5" s="1">
+        <v>0</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="N5" s="1">
+        <v>0</v>
+      </c>
+      <c r="O5" s="1">
+        <v>0</v>
+      </c>
+      <c r="P5" s="1">
+        <v>0</v>
+      </c>
       <c r="Q5" s="1">
+        <v>0</v>
+      </c>
+      <c r="R5" s="1">
         <v>977</v>
-      </c>
-      <c r="R5" s="1" t="s">
-        <v>26</v>
       </c>
       <c r="S5" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="T5" s="1"/>
+      <c r="T5" s="1" t="s">
+        <v>28</v>
+      </c>
       <c r="U5" s="1"/>
-      <c r="V5" s="1">
+      <c r="V5" s="1"/>
+      <c r="W5" s="1">
         <v>1234567898</v>
       </c>
     </row>
-    <row r="6" spans="1:22">
+    <row r="6" spans="1:23">
       <c r="A6" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B6" s="1">
         <v>3000</v>
@@ -857,31 +887,42 @@
       <c r="K6" s="1">
         <v>0.0</v>
       </c>
-      <c r="L6" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="M6" s="1"/>
-      <c r="N6" s="1"/>
-      <c r="O6" s="1"/>
-      <c r="P6" s="1"/>
+      <c r="L6" s="1">
+        <v>0</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="N6" s="1">
+        <v>0</v>
+      </c>
+      <c r="O6" s="1">
+        <v>0</v>
+      </c>
+      <c r="P6" s="1">
+        <v>0</v>
+      </c>
       <c r="Q6" s="1">
+        <v>0</v>
+      </c>
+      <c r="R6" s="1">
         <v>865</v>
-      </c>
-      <c r="R6" s="1" t="s">
-        <v>26</v>
       </c>
       <c r="S6" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="T6" s="1"/>
+      <c r="T6" s="1" t="s">
+        <v>28</v>
+      </c>
       <c r="U6" s="1"/>
-      <c r="V6" s="1">
+      <c r="V6" s="1"/>
+      <c r="W6" s="1">
         <v>1234567898</v>
       </c>
     </row>
-    <row r="7" spans="1:22">
+    <row r="7" spans="1:23">
       <c r="A7" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B7" s="1">
         <v>3000</v>
@@ -913,31 +954,42 @@
       <c r="K7" s="1">
         <v>0.0</v>
       </c>
-      <c r="L7" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="M7" s="1"/>
-      <c r="N7" s="1"/>
-      <c r="O7" s="1"/>
-      <c r="P7" s="1"/>
+      <c r="L7" s="1">
+        <v>0</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="N7" s="1">
+        <v>0</v>
+      </c>
+      <c r="O7" s="1">
+        <v>0</v>
+      </c>
+      <c r="P7" s="1">
+        <v>0</v>
+      </c>
       <c r="Q7" s="1">
+        <v>0</v>
+      </c>
+      <c r="R7" s="1">
         <v>499</v>
-      </c>
-      <c r="R7" s="1" t="s">
-        <v>26</v>
       </c>
       <c r="S7" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="T7" s="1"/>
+      <c r="T7" s="1" t="s">
+        <v>28</v>
+      </c>
       <c r="U7" s="1"/>
-      <c r="V7" s="1">
+      <c r="V7" s="1"/>
+      <c r="W7" s="1">
         <v>1234567898</v>
       </c>
     </row>
-    <row r="8" spans="1:22">
+    <row r="8" spans="1:23">
       <c r="A8" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B8" s="1">
         <v>3000</v>
@@ -969,31 +1021,42 @@
       <c r="K8" s="1">
         <v>0.0</v>
       </c>
-      <c r="L8" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="M8" s="1"/>
-      <c r="N8" s="1"/>
-      <c r="O8" s="1"/>
-      <c r="P8" s="1"/>
+      <c r="L8" s="1">
+        <v>1600.0</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="N8" s="1">
+        <v>0</v>
+      </c>
+      <c r="O8" s="1">
+        <v>0</v>
+      </c>
+      <c r="P8" s="1">
+        <v>0</v>
+      </c>
       <c r="Q8" s="1">
+        <v>0</v>
+      </c>
+      <c r="R8" s="1">
         <v>1063</v>
-      </c>
-      <c r="R8" s="1" t="s">
-        <v>36</v>
       </c>
       <c r="S8" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="T8" s="1"/>
+      <c r="T8" s="1" t="s">
+        <v>38</v>
+      </c>
       <c r="U8" s="1"/>
-      <c r="V8" s="1">
+      <c r="V8" s="1"/>
+      <c r="W8" s="1">
         <v>1111111111</v>
       </c>
     </row>
-    <row r="9" spans="1:22">
+    <row r="9" spans="1:23">
       <c r="A9" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B9" s="1">
         <v>3000</v>
@@ -1025,31 +1088,42 @@
       <c r="K9" s="1">
         <v>0.0</v>
       </c>
-      <c r="L9" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="M9" s="1"/>
-      <c r="N9" s="1"/>
-      <c r="O9" s="1"/>
-      <c r="P9" s="1"/>
+      <c r="L9" s="1">
+        <v>1600.0</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="N9" s="1">
+        <v>0</v>
+      </c>
+      <c r="O9" s="1">
+        <v>0</v>
+      </c>
+      <c r="P9" s="1">
+        <v>0</v>
+      </c>
       <c r="Q9" s="1">
+        <v>0</v>
+      </c>
+      <c r="R9" s="1">
         <v>1314</v>
-      </c>
-      <c r="R9" s="1" t="s">
-        <v>40</v>
       </c>
       <c r="S9" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="T9" s="1"/>
+      <c r="T9" s="1" t="s">
+        <v>42</v>
+      </c>
       <c r="U9" s="1"/>
-      <c r="V9" s="1">
+      <c r="V9" s="1"/>
+      <c r="W9" s="1">
         <v>7854547777</v>
       </c>
     </row>
-    <row r="10" spans="1:22">
+    <row r="10" spans="1:23">
       <c r="A10" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B10" s="1">
         <v>5000</v>
@@ -1081,33 +1155,42 @@
       <c r="K10" s="1">
         <v>0.0</v>
       </c>
-      <c r="L10" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="M10" s="1"/>
-      <c r="N10" s="1"/>
+      <c r="L10" s="1">
+        <v>0</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="N10" s="1">
+        <v>0</v>
+      </c>
       <c r="O10" s="1">
+        <v>0</v>
+      </c>
+      <c r="P10" s="1">
         <v>10</v>
       </c>
-      <c r="P10" s="1"/>
       <c r="Q10" s="1">
+        <v>0</v>
+      </c>
+      <c r="R10" s="1">
         <v>1400</v>
-      </c>
-      <c r="R10" s="1" t="s">
-        <v>44</v>
       </c>
       <c r="S10" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="T10" s="1"/>
+      <c r="T10" s="1" t="s">
+        <v>46</v>
+      </c>
       <c r="U10" s="1"/>
-      <c r="V10" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="11" spans="1:22">
+      <c r="V10" s="1"/>
+      <c r="W10" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23">
       <c r="A11" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B11" s="1">
         <v>3000</v>
@@ -1139,31 +1222,42 @@
       <c r="K11" s="1">
         <v>0.0</v>
       </c>
-      <c r="L11" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="M11" s="1"/>
-      <c r="N11" s="1"/>
-      <c r="O11" s="1"/>
-      <c r="P11" s="1"/>
+      <c r="L11" s="1">
+        <v>1050.0</v>
+      </c>
+      <c r="M11" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="N11" s="1">
+        <v>0</v>
+      </c>
+      <c r="O11" s="1">
+        <v>0</v>
+      </c>
+      <c r="P11" s="1">
+        <v>0</v>
+      </c>
       <c r="Q11" s="1">
+        <v>0</v>
+      </c>
+      <c r="R11" s="1">
         <v>512</v>
-      </c>
-      <c r="R11" s="1" t="s">
-        <v>49</v>
       </c>
       <c r="S11" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="T11" s="1"/>
+      <c r="T11" s="1" t="s">
+        <v>51</v>
+      </c>
       <c r="U11" s="1"/>
-      <c r="V11" s="1">
+      <c r="V11" s="1"/>
+      <c r="W11" s="1">
         <v>1231516516</v>
       </c>
     </row>
-    <row r="12" spans="1:22">
+    <row r="12" spans="1:23">
       <c r="A12" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B12" s="1">
         <v>3000</v>
@@ -1195,33 +1289,42 @@
       <c r="K12" s="1">
         <v>0.0</v>
       </c>
-      <c r="L12" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="M12" s="1"/>
-      <c r="N12" s="1"/>
+      <c r="L12" s="1">
+        <v>1050.0</v>
+      </c>
+      <c r="M12" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="N12" s="1">
+        <v>0</v>
+      </c>
       <c r="O12" s="1">
+        <v>0</v>
+      </c>
+      <c r="P12" s="1">
         <v>695</v>
       </c>
-      <c r="P12" s="1"/>
       <c r="Q12" s="1">
+        <v>0</v>
+      </c>
+      <c r="R12" s="1">
         <v>695</v>
-      </c>
-      <c r="R12" s="1" t="s">
-        <v>49</v>
       </c>
       <c r="S12" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="T12" s="1"/>
+      <c r="T12" s="1" t="s">
+        <v>51</v>
+      </c>
       <c r="U12" s="1"/>
-      <c r="V12" s="1">
+      <c r="V12" s="1"/>
+      <c r="W12" s="1">
         <v>1231516516</v>
       </c>
     </row>
-    <row r="13" spans="1:22">
+    <row r="13" spans="1:23">
       <c r="A13" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B13" s="1">
         <v>3000</v>
@@ -1253,33 +1356,42 @@
       <c r="K13" s="1">
         <v>0.0</v>
       </c>
-      <c r="L13" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="M13" s="1"/>
-      <c r="N13" s="1"/>
+      <c r="L13" s="1">
+        <v>1050.0</v>
+      </c>
+      <c r="M13" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="N13" s="1">
+        <v>0</v>
+      </c>
       <c r="O13" s="1">
+        <v>0</v>
+      </c>
+      <c r="P13" s="1">
         <v>60</v>
       </c>
-      <c r="P13" s="1"/>
       <c r="Q13" s="1">
+        <v>0</v>
+      </c>
+      <c r="R13" s="1">
         <v>1776</v>
-      </c>
-      <c r="R13" s="1" t="s">
-        <v>49</v>
       </c>
       <c r="S13" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="T13" s="1"/>
+      <c r="T13" s="1" t="s">
+        <v>51</v>
+      </c>
       <c r="U13" s="1"/>
-      <c r="V13" s="1">
+      <c r="V13" s="1"/>
+      <c r="W13" s="1">
         <v>1231516516</v>
       </c>
     </row>
-    <row r="14" spans="1:22">
+    <row r="14" spans="1:23">
       <c r="A14" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B14" s="1">
         <v>5000</v>
@@ -1311,33 +1423,42 @@
       <c r="K14" s="1">
         <v>0.0</v>
       </c>
-      <c r="L14" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="M14" s="1"/>
-      <c r="N14" s="1"/>
+      <c r="L14" s="1">
+        <v>0</v>
+      </c>
+      <c r="M14" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="N14" s="1">
+        <v>0</v>
+      </c>
       <c r="O14" s="1">
+        <v>0</v>
+      </c>
+      <c r="P14" s="1">
         <v>113</v>
       </c>
-      <c r="P14" s="1"/>
       <c r="Q14" s="1">
+        <v>0</v>
+      </c>
+      <c r="R14" s="1">
         <v>1522</v>
-      </c>
-      <c r="R14" s="1" t="s">
-        <v>44</v>
       </c>
       <c r="S14" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="T14" s="1"/>
+      <c r="T14" s="1" t="s">
+        <v>46</v>
+      </c>
       <c r="U14" s="1"/>
-      <c r="V14" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="15" spans="1:22">
+      <c r="V14" s="1"/>
+      <c r="W14" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23">
       <c r="A15" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B15" s="1">
         <v>3000</v>
@@ -1369,31 +1490,42 @@
       <c r="K15" s="1">
         <v>0.0</v>
       </c>
-      <c r="L15" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="M15" s="1"/>
-      <c r="N15" s="1"/>
-      <c r="O15" s="1"/>
-      <c r="P15" s="1"/>
+      <c r="L15" s="1">
+        <v>0</v>
+      </c>
+      <c r="M15" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="N15" s="1">
+        <v>0</v>
+      </c>
+      <c r="O15" s="1">
+        <v>0</v>
+      </c>
+      <c r="P15" s="1">
+        <v>0</v>
+      </c>
       <c r="Q15" s="1">
+        <v>0</v>
+      </c>
+      <c r="R15" s="1">
         <v>331</v>
-      </c>
-      <c r="R15" s="1" t="s">
-        <v>40</v>
       </c>
       <c r="S15" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="T15" s="1"/>
+      <c r="T15" s="1" t="s">
+        <v>42</v>
+      </c>
       <c r="U15" s="1"/>
-      <c r="V15" s="1">
+      <c r="V15" s="1"/>
+      <c r="W15" s="1">
         <v>7854547777</v>
       </c>
     </row>
-    <row r="16" spans="1:22">
+    <row r="16" spans="1:23">
       <c r="A16" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B16" s="1">
         <v>3000</v>
@@ -1425,31 +1557,42 @@
       <c r="K16" s="1">
         <v>0.0</v>
       </c>
-      <c r="L16" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="M16" s="1"/>
-      <c r="N16" s="1"/>
-      <c r="O16" s="1"/>
-      <c r="P16" s="1"/>
+      <c r="L16" s="1">
+        <v>0</v>
+      </c>
+      <c r="M16" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="N16" s="1">
+        <v>0</v>
+      </c>
+      <c r="O16" s="1">
+        <v>0</v>
+      </c>
+      <c r="P16" s="1">
+        <v>0</v>
+      </c>
       <c r="Q16" s="1">
+        <v>0</v>
+      </c>
+      <c r="R16" s="1">
         <v>383</v>
       </c>
-      <c r="R16" s="1" t="s">
-        <v>61</v>
-      </c>
       <c r="S16" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="T16" s="1"/>
+        <v>62</v>
+      </c>
+      <c r="T16" s="1" t="s">
+        <v>46</v>
+      </c>
       <c r="U16" s="1"/>
-      <c r="V16" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="17" spans="1:22">
+      <c r="V16" s="1"/>
+      <c r="W16" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="17" spans="1:23">
       <c r="A17" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B17" s="1">
         <v>3000</v>
@@ -1481,31 +1624,42 @@
       <c r="K17" s="1">
         <v>0.0</v>
       </c>
-      <c r="L17" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="M17" s="1"/>
-      <c r="N17" s="1"/>
-      <c r="O17" s="1"/>
-      <c r="P17" s="1"/>
+      <c r="L17" s="1">
+        <v>1050.0</v>
+      </c>
+      <c r="M17" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="N17" s="1">
+        <v>0</v>
+      </c>
+      <c r="O17" s="1">
+        <v>0</v>
+      </c>
+      <c r="P17" s="1">
+        <v>0</v>
+      </c>
       <c r="Q17" s="1">
+        <v>0</v>
+      </c>
+      <c r="R17" s="1">
         <v>761</v>
-      </c>
-      <c r="R17" s="1" t="s">
-        <v>49</v>
       </c>
       <c r="S17" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="T17" s="1"/>
+      <c r="T17" s="1" t="s">
+        <v>51</v>
+      </c>
       <c r="U17" s="1"/>
-      <c r="V17" s="1">
+      <c r="V17" s="1"/>
+      <c r="W17" s="1">
         <v>1231516516</v>
       </c>
     </row>
-    <row r="18" spans="1:22">
+    <row r="18" spans="1:23">
       <c r="A18" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B18" s="1">
         <v>5000</v>
@@ -1535,31 +1689,40 @@
       <c r="K18" s="1">
         <v>0.0</v>
       </c>
-      <c r="L18" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="M18" s="1"/>
-      <c r="N18" s="1"/>
+      <c r="L18" s="1">
+        <v>250.0</v>
+      </c>
+      <c r="M18" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="N18" s="1">
+        <v>0</v>
+      </c>
       <c r="O18" s="1">
+        <v>0</v>
+      </c>
+      <c r="P18" s="1">
         <v>14</v>
       </c>
-      <c r="P18" s="1"/>
-      <c r="Q18" s="1"/>
-      <c r="R18" s="1" t="s">
-        <v>66</v>
-      </c>
+      <c r="Q18" s="1">
+        <v>0</v>
+      </c>
+      <c r="R18" s="1"/>
       <c r="S18" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="T18" s="1"/>
+        <v>67</v>
+      </c>
+      <c r="T18" s="1" t="s">
+        <v>46</v>
+      </c>
       <c r="U18" s="1"/>
-      <c r="V18" s="1">
+      <c r="V18" s="1"/>
+      <c r="W18" s="1">
         <v>4854746554</v>
       </c>
     </row>
-    <row r="19" spans="1:22">
+    <row r="19" spans="1:23">
       <c r="A19" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B19" s="1">
         <v>5000</v>
@@ -1591,33 +1754,42 @@
       <c r="K19" s="1">
         <v>0.0</v>
       </c>
-      <c r="L19" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="M19" s="1"/>
-      <c r="N19" s="1"/>
+      <c r="L19" s="1">
+        <v>1100.0</v>
+      </c>
+      <c r="M19" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="N19" s="1">
+        <v>0</v>
+      </c>
       <c r="O19" s="1">
+        <v>0</v>
+      </c>
+      <c r="P19" s="1">
         <v>12</v>
       </c>
-      <c r="P19" s="1"/>
       <c r="Q19" s="1">
+        <v>0</v>
+      </c>
+      <c r="R19" s="1">
         <v>657</v>
       </c>
-      <c r="R19" s="1" t="s">
-        <v>66</v>
-      </c>
       <c r="S19" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="T19" s="1"/>
+        <v>67</v>
+      </c>
+      <c r="T19" s="1" t="s">
+        <v>46</v>
+      </c>
       <c r="U19" s="1"/>
-      <c r="V19" s="1">
+      <c r="V19" s="1"/>
+      <c r="W19" s="1">
         <v>4854746554</v>
       </c>
     </row>
-    <row r="20" spans="1:22">
+    <row r="20" spans="1:23">
       <c r="A20" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B20" s="1">
         <v>5000</v>
@@ -1649,33 +1821,42 @@
       <c r="K20" s="1">
         <v>0.0</v>
       </c>
-      <c r="L20" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="M20" s="1"/>
-      <c r="N20" s="1"/>
+      <c r="L20" s="1">
+        <v>1600.0</v>
+      </c>
+      <c r="M20" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="N20" s="1">
+        <v>0</v>
+      </c>
       <c r="O20" s="1">
+        <v>0</v>
+      </c>
+      <c r="P20" s="1">
         <v>6</v>
       </c>
-      <c r="P20" s="1"/>
       <c r="Q20" s="1">
+        <v>0</v>
+      </c>
+      <c r="R20" s="1">
         <v>471</v>
-      </c>
-      <c r="R20" s="1" t="s">
-        <v>71</v>
       </c>
       <c r="S20" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="T20" s="1"/>
+      <c r="T20" s="1" t="s">
+        <v>73</v>
+      </c>
       <c r="U20" s="1"/>
-      <c r="V20" s="1">
+      <c r="V20" s="1"/>
+      <c r="W20" s="1">
         <v>1111111111</v>
       </c>
     </row>
-    <row r="21" spans="1:22">
+    <row r="21" spans="1:23">
       <c r="A21" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B21" s="1">
         <v>5000</v>
@@ -1707,33 +1888,42 @@
       <c r="K21" s="1">
         <v>0.0</v>
       </c>
-      <c r="L21" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="M21" s="1"/>
-      <c r="N21" s="1"/>
+      <c r="L21" s="1">
+        <v>2100.0</v>
+      </c>
+      <c r="M21" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="N21" s="1">
+        <v>0</v>
+      </c>
       <c r="O21" s="1">
+        <v>0</v>
+      </c>
+      <c r="P21" s="1">
         <v>3</v>
       </c>
-      <c r="P21" s="1"/>
       <c r="Q21" s="1">
+        <v>0</v>
+      </c>
+      <c r="R21" s="1">
         <v>1677</v>
-      </c>
-      <c r="R21" s="1" t="s">
-        <v>71</v>
       </c>
       <c r="S21" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="T21" s="1"/>
+      <c r="T21" s="1" t="s">
+        <v>73</v>
+      </c>
       <c r="U21" s="1"/>
-      <c r="V21" s="1">
+      <c r="V21" s="1"/>
+      <c r="W21" s="1">
         <v>1111111111</v>
       </c>
     </row>
-    <row r="22" spans="1:22">
+    <row r="22" spans="1:23">
       <c r="A22" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B22" s="1">
         <v>5000</v>
@@ -1765,33 +1955,42 @@
       <c r="K22" s="1">
         <v>0.0</v>
       </c>
-      <c r="L22" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="M22" s="1"/>
-      <c r="N22" s="1"/>
+      <c r="L22" s="1">
+        <v>0</v>
+      </c>
+      <c r="M22" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="N22" s="1">
+        <v>0</v>
+      </c>
       <c r="O22" s="1">
+        <v>0</v>
+      </c>
+      <c r="P22" s="1">
         <v>10</v>
       </c>
-      <c r="P22" s="1"/>
       <c r="Q22" s="1">
+        <v>0</v>
+      </c>
+      <c r="R22" s="1">
         <v>1400</v>
-      </c>
-      <c r="R22" s="1" t="s">
-        <v>71</v>
       </c>
       <c r="S22" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="T22" s="1"/>
+      <c r="T22" s="1" t="s">
+        <v>73</v>
+      </c>
       <c r="U22" s="1"/>
-      <c r="V22" s="1">
+      <c r="V22" s="1"/>
+      <c r="W22" s="1">
         <v>1111111111</v>
       </c>
     </row>
-    <row r="23" spans="1:22">
+    <row r="23" spans="1:23">
       <c r="A23" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B23" s="1">
         <v>5000</v>
@@ -1823,27 +2022,36 @@
       <c r="K23" s="1">
         <v>0.0</v>
       </c>
-      <c r="L23" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="M23" s="1"/>
-      <c r="N23" s="1"/>
+      <c r="L23" s="1">
+        <v>0</v>
+      </c>
+      <c r="M23" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="N23" s="1">
+        <v>0</v>
+      </c>
       <c r="O23" s="1">
+        <v>0</v>
+      </c>
+      <c r="P23" s="1">
         <v>113</v>
       </c>
-      <c r="P23" s="1"/>
       <c r="Q23" s="1">
+        <v>0</v>
+      </c>
+      <c r="R23" s="1">
         <v>1493</v>
-      </c>
-      <c r="R23" s="1" t="s">
-        <v>71</v>
       </c>
       <c r="S23" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="T23" s="1"/>
+      <c r="T23" s="1" t="s">
+        <v>73</v>
+      </c>
       <c r="U23" s="1"/>
-      <c r="V23" s="1">
+      <c r="V23" s="1"/>
+      <c r="W23" s="1">
         <v>1111111111</v>
       </c>
     </row>
